--- a/clientes.xlsx
+++ b/clientes.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\LENOVO\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\laragon\www\condominioterrazas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7809F4C9-93B3-4C74-B0C8-DAA98B128082}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{75DB62CC-E136-46C1-9CB3-4A3EBB9CA0F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{C55A2232-87D0-41ED-9212-52063D1711C8}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="19">
   <si>
     <t>DNI</t>
   </si>
@@ -84,6 +84,15 @@
   </si>
   <si>
     <t>Jose Luis</t>
+  </si>
+  <si>
+    <t>Jose</t>
+  </si>
+  <si>
+    <t>Perez</t>
+  </si>
+  <si>
+    <t>joseperez@gmail.com</t>
   </si>
 </sst>
 </file>
@@ -466,7 +475,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BD0B8B2F-9FA7-4717-8301-335C9528E270}">
-  <dimension ref="A1:H6"/>
+  <dimension ref="A1:H7"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="8" width="23.33203125" customWidth="1"/>
@@ -628,6 +637,32 @@
         <v>9</v>
       </c>
     </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A7">
+        <v>99999999</v>
+      </c>
+      <c r="B7" t="s">
+        <v>16</v>
+      </c>
+      <c r="C7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D7">
+        <v>999999999</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="F7">
+        <v>3</v>
+      </c>
+      <c r="G7">
+        <v>1</v>
+      </c>
+      <c r="H7" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="E2" r:id="rId1" xr:uid="{4B8397F1-3A98-4BFF-82AF-19AD53695E25}"/>
@@ -635,6 +670,7 @@
     <hyperlink ref="E4" r:id="rId3" xr:uid="{542C51AF-9FA1-4FAC-8675-8C753EAE104C}"/>
     <hyperlink ref="E5" r:id="rId4" xr:uid="{142A1FD1-C780-49BD-8867-8FC0E372A449}"/>
     <hyperlink ref="E6" r:id="rId5" xr:uid="{76649BCD-034B-48B4-942A-0EAB71E1EB41}"/>
+    <hyperlink ref="E7" r:id="rId6" xr:uid="{83DC1F5D-FC83-438D-AEFF-970C3782776F}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/clientes.xlsx
+++ b/clientes.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\laragon\www\condominioterrazas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{75DB62CC-E136-46C1-9CB3-4A3EBB9CA0F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{389F5CEC-2AC5-4B07-A7DE-C4315CF4B3E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{C55A2232-87D0-41ED-9212-52063D1711C8}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="20">
   <si>
     <t>DNI</t>
   </si>
@@ -93,6 +93,9 @@
   </si>
   <si>
     <t>joseperez@gmail.com</t>
+  </si>
+  <si>
+    <t>J21</t>
   </si>
 </sst>
 </file>
@@ -475,7 +478,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BD0B8B2F-9FA7-4717-8301-335C9528E270}">
-  <dimension ref="A1:H7"/>
+  <dimension ref="A1:H9"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="8" width="23.33203125" customWidth="1"/>
@@ -663,6 +666,50 @@
         <v>7</v>
       </c>
     </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A8">
+        <v>99999999</v>
+      </c>
+      <c r="B8" t="s">
+        <v>16</v>
+      </c>
+      <c r="C8" t="s">
+        <v>17</v>
+      </c>
+      <c r="D8">
+        <v>999999999</v>
+      </c>
+      <c r="E8" s="1"/>
+      <c r="F8">
+        <v>3</v>
+      </c>
+      <c r="G8">
+        <v>1</v>
+      </c>
+      <c r="H8" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A9">
+        <v>99999999</v>
+      </c>
+      <c r="B9" t="s">
+        <v>16</v>
+      </c>
+      <c r="C9" t="s">
+        <v>17</v>
+      </c>
+      <c r="D9">
+        <v>999999999</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="G9">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="E2" r:id="rId1" xr:uid="{4B8397F1-3A98-4BFF-82AF-19AD53695E25}"/>
@@ -671,6 +718,7 @@
     <hyperlink ref="E5" r:id="rId4" xr:uid="{142A1FD1-C780-49BD-8867-8FC0E372A449}"/>
     <hyperlink ref="E6" r:id="rId5" xr:uid="{76649BCD-034B-48B4-942A-0EAB71E1EB41}"/>
     <hyperlink ref="E7" r:id="rId6" xr:uid="{83DC1F5D-FC83-438D-AEFF-970C3782776F}"/>
+    <hyperlink ref="E9" r:id="rId7" xr:uid="{7CC671D5-0348-4465-A931-8BAD6878A515}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/clientes.xlsx
+++ b/clientes.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\laragon\www\condominioterrazas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{389F5CEC-2AC5-4B07-A7DE-C4315CF4B3E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9E5D66B3-D35E-40B1-B7DF-D8E2B6CC0EA9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{C55A2232-87D0-41ED-9212-52063D1711C8}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="25">
   <si>
     <t>DNI</t>
   </si>
@@ -96,6 +96,21 @@
   </si>
   <si>
     <t>J21</t>
+  </si>
+  <si>
+    <t>Pedro</t>
+  </si>
+  <si>
+    <t>Sanchez</t>
+  </si>
+  <si>
+    <t>pedrosanchez@gmail.com</t>
+  </si>
+  <si>
+    <t>J1</t>
+  </si>
+  <si>
+    <t>Fecha</t>
   </si>
 </sst>
 </file>
@@ -140,9 +155,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hipervínculo" xfId="1" builtinId="8"/>
@@ -478,13 +494,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BD0B8B2F-9FA7-4717-8301-335C9528E270}">
-  <dimension ref="A1:H9"/>
+  <dimension ref="A1:I10"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="8" width="23.33203125" customWidth="1"/>
+    <col min="1" max="9" width="23.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -501,16 +517,19 @@
         <v>10</v>
       </c>
       <c r="F1" t="s">
+        <v>24</v>
+      </c>
+      <c r="G1" t="s">
         <v>2</v>
       </c>
-      <c r="G1" t="s">
-        <v>3</v>
-      </c>
       <c r="H1" t="s">
+        <v>3</v>
+      </c>
+      <c r="I1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>47753898</v>
       </c>
@@ -526,17 +545,20 @@
       <c r="E2" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="F2">
-        <v>3</v>
+      <c r="F2" s="2">
+        <v>46084</v>
       </c>
       <c r="G2">
-        <v>1</v>
-      </c>
-      <c r="H2" t="s">
+        <v>3</v>
+      </c>
+      <c r="H2">
+        <v>1</v>
+      </c>
+      <c r="I2" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>47753898</v>
       </c>
@@ -552,17 +574,20 @@
       <c r="E3" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="F3">
-        <v>3</v>
+      <c r="F3" s="2">
+        <v>46084</v>
       </c>
       <c r="G3">
-        <v>1</v>
-      </c>
-      <c r="H3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H3">
+        <v>1</v>
+      </c>
+      <c r="I3" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>47753898</v>
       </c>
@@ -578,17 +603,20 @@
       <c r="E4" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="F4">
-        <v>3</v>
+      <c r="F4" s="2">
+        <v>46084</v>
       </c>
       <c r="G4">
-        <v>1</v>
-      </c>
-      <c r="H4" t="s">
+        <v>3</v>
+      </c>
+      <c r="H4">
+        <v>1</v>
+      </c>
+      <c r="I4" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>47753898</v>
       </c>
@@ -604,17 +632,20 @@
       <c r="E5" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="F5">
-        <v>3</v>
+      <c r="F5" s="2">
+        <v>46115</v>
       </c>
       <c r="G5">
-        <v>1</v>
-      </c>
-      <c r="H5" t="s">
+        <v>3</v>
+      </c>
+      <c r="H5">
+        <v>1</v>
+      </c>
+      <c r="I5" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>47753898</v>
       </c>
@@ -630,17 +661,20 @@
       <c r="E6" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="F6">
-        <v>3</v>
+      <c r="F6" s="2">
+        <v>46145</v>
       </c>
       <c r="G6">
-        <v>1</v>
-      </c>
-      <c r="H6" t="s">
+        <v>3</v>
+      </c>
+      <c r="H6">
+        <v>1</v>
+      </c>
+      <c r="I6" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>99999999</v>
       </c>
@@ -656,17 +690,20 @@
       <c r="E7" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="F7">
-        <v>3</v>
+      <c r="F7" s="2">
+        <v>46115</v>
       </c>
       <c r="G7">
-        <v>1</v>
-      </c>
-      <c r="H7" t="s">
+        <v>3</v>
+      </c>
+      <c r="H7">
+        <v>1</v>
+      </c>
+      <c r="I7" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>99999999</v>
       </c>
@@ -680,17 +717,20 @@
         <v>999999999</v>
       </c>
       <c r="E8" s="1"/>
-      <c r="F8">
-        <v>3</v>
+      <c r="F8" s="2">
+        <v>46025</v>
       </c>
       <c r="G8">
-        <v>1</v>
-      </c>
-      <c r="H8" t="s">
+        <v>3</v>
+      </c>
+      <c r="H8">
+        <v>1</v>
+      </c>
+      <c r="I8" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>99999999</v>
       </c>
@@ -706,8 +746,40 @@
       <c r="E9" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="G9">
-        <v>1</v>
+      <c r="F9" s="2">
+        <v>46056</v>
+      </c>
+      <c r="H9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A10">
+        <v>11111111</v>
+      </c>
+      <c r="B10" t="s">
+        <v>20</v>
+      </c>
+      <c r="C10" t="s">
+        <v>21</v>
+      </c>
+      <c r="D10">
+        <v>888888888</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="F10" s="2">
+        <v>46084</v>
+      </c>
+      <c r="G10">
+        <v>3</v>
+      </c>
+      <c r="H10">
+        <v>2</v>
+      </c>
+      <c r="I10" t="s">
+        <v>23</v>
       </c>
     </row>
   </sheetData>
@@ -719,6 +791,7 @@
     <hyperlink ref="E6" r:id="rId5" xr:uid="{76649BCD-034B-48B4-942A-0EAB71E1EB41}"/>
     <hyperlink ref="E7" r:id="rId6" xr:uid="{83DC1F5D-FC83-438D-AEFF-970C3782776F}"/>
     <hyperlink ref="E9" r:id="rId7" xr:uid="{7CC671D5-0348-4465-A931-8BAD6878A515}"/>
+    <hyperlink ref="E10" r:id="rId8" xr:uid="{75D76FAB-D61D-473C-BB28-88B3090C7A09}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/clientes.xlsx
+++ b/clientes.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\laragon\www\condominioterrazas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9E5D66B3-D35E-40B1-B7DF-D8E2B6CC0EA9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{44523FBC-CF45-49E5-B814-E6CFE942332A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{C55A2232-87D0-41ED-9212-52063D1711C8}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="29">
   <si>
     <t>DNI</t>
   </si>
@@ -111,6 +111,18 @@
   </si>
   <si>
     <t>Fecha</t>
+  </si>
+  <si>
+    <t>juan</t>
+  </si>
+  <si>
+    <t>lucas</t>
+  </si>
+  <si>
+    <t>juanlucas@gmail.com</t>
+  </si>
+  <si>
+    <t>J2</t>
   </si>
 </sst>
 </file>
@@ -494,7 +506,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BD0B8B2F-9FA7-4717-8301-335C9528E270}">
-  <dimension ref="A1:I10"/>
+  <dimension ref="A1:I11"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="9" width="23.33203125" customWidth="1"/>
@@ -780,6 +792,35 @@
       </c>
       <c r="I10" t="s">
         <v>23</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A11">
+        <v>12345678</v>
+      </c>
+      <c r="B11" t="s">
+        <v>25</v>
+      </c>
+      <c r="C11" t="s">
+        <v>26</v>
+      </c>
+      <c r="D11">
+        <v>111111111</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F11" s="2">
+        <v>46147</v>
+      </c>
+      <c r="G11">
+        <v>3</v>
+      </c>
+      <c r="H11">
+        <v>1</v>
+      </c>
+      <c r="I11" t="s">
+        <v>28</v>
       </c>
     </row>
   </sheetData>
@@ -792,6 +833,7 @@
     <hyperlink ref="E7" r:id="rId6" xr:uid="{83DC1F5D-FC83-438D-AEFF-970C3782776F}"/>
     <hyperlink ref="E9" r:id="rId7" xr:uid="{7CC671D5-0348-4465-A931-8BAD6878A515}"/>
     <hyperlink ref="E10" r:id="rId8" xr:uid="{75D76FAB-D61D-473C-BB28-88B3090C7A09}"/>
+    <hyperlink ref="E11" r:id="rId9" xr:uid="{0CDB362E-B24C-4AEE-B16F-1A12040DA854}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
